--- a/docs/assets/konusarak-ogren-hr-outbound-google-sheets.xlsx
+++ b/docs/assets/konusarak-ogren-hr-outbound-google-sheets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HR Leads" sheetId="1" r:id="R83c7f3018f6542e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow" sheetId="2" r:id="R1597296d671346f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HR Leads" sheetId="1" r:id="R3dc8e5542dc74f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow" sheetId="2" r:id="R24651fb69dea4275"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -194,7 +194,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Ad Soyad</x:v>
+        <x:v>﻿Ad Soyad</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Şirket</x:v>
@@ -235,255 +235,255 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>Derya Yilmaz</x:v>
+        <x:v>Irem Kilic</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D2" t="str"/>
       <x:c r="E2" t="str"/>
       <x:c r="F2" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>76</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>Merhaba Derya, Yemeksepeti için Human Resources Director rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Irem, Garanti BBVA icin Insan Kaynaklari Muduru rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Derya,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Irem,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>Mehmet Ozturk</x:v>
+        <x:v>Asli Yildiz</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>Turkcell</x:v>
+        <x:v>Papara</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D3" t="str"/>
       <x:c r="E3" t="str"/>
       <x:c r="F3" t="str">
-        <x:v>Telecommunications</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>Merhaba Mehmet, Turkcell için Organizational Development Manager rolünüzü gördüm. Telecommunications tarafında kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Asli, Papara icin Talent Management Specialist rolunuzu gordum. Fintech tarafinda fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>Subject: Turkcell ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Turkcell ekibinin Telecommunications ölçeğinde kurumsal dönüşüm ve teknoloji yetkinlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Turkcell için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Papara ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Asli,
+Papara ekibinin Fintech olceginde fintech buyumesi ve regulasyonla uyumlu ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Papara icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>Elif Kaya</x:v>
+        <x:v>Ece Yildiz</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D4" t="str"/>
       <x:c r="E4" t="str"/>
       <x:c r="F4" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>Merhaba Elif, Ford Otosan için Employee Experience Lead rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ece, Mavi icin Talent Acquisition Manager rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ece,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>Mehmet Sahin</x:v>
+        <x:v>Ece Yilmaz</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>LC Waikiki</x:v>
+        <x:v>Vodafone Turkey</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D5" t="str"/>
       <x:c r="E5" t="str"/>
       <x:c r="F5" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Telecommunications</x:v>
       </x:c>
       <x:c r="G5" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H5" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>global ekiplerle yogun is birligi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>73</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>Merhaba Mehmet, LC Waikiki için HR Business Partner rolünüzü gördüm. Retail / Fashion tarafında mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ece, Vodafone Turkey icin Insan Kaynaklari Uzmani rolunuzu gordum. Telecommunications tarafinda global ekiplerle yogun is birligi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global ekiplerle yogun is birligi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L5" t="str">
-        <x:v>Subject: LC Waikiki ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-LC Waikiki ekibinin Retail / Fashion ölçeğinde mağaza, merkez ve yurt dışı perakende operasyonları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede LC Waikiki için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Vodafone Turkey ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ece,
+Vodafone Turkey ekibinin Telecommunications olceginde global ekiplerle yogun is birligi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global ekiplerle yogun is birligi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Vodafone Turkey icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M5" t="str">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>Derya Yildiz</x:v>
+        <x:v>Kerem Bulut</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Trendyol</x:v>
+        <x:v>Ford Otosan</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D6" t="str"/>
       <x:c r="E6" t="str"/>
       <x:c r="F6" t="str">
-        <x:v>E-commerce / Marketplace</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G6" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H6" t="str">
-        <x:v>hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I6" t="str">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>Merhaba Derya, Trendyol için Human Resources Director rolünüzü gördüm. E-commerce / Marketplace tarafında hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Ford Otosan icin Learning and Development Manager rolunuzu gordum. Automotive / Manufacturing tarafinda uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L6" t="str">
-        <x:v>Subject: Trendyol ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Derya,
-Trendyol ekibinin E-commerce / Marketplace ölçeğinde hızlı ölçeklenen ekipler ve uluslararası operasyon odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Trendyol için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Ford Otosan ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Ford Otosan ekibinin Automotive / Manufacturing olceginde uretim, muhendislik ve global tedarik zinciri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Ford Otosan icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M6" t="str">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Onur Sahin</x:v>
+        <x:v>Onur Kaya</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Sabanci Holding</x:v>
+        <x:v>Getir</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D7" t="str"/>
       <x:c r="E7" t="str"/>
       <x:c r="F7" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>Quick commerce / Delivery</x:v>
       </x:c>
       <x:c r="G7" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H7" t="str">
-        <x:v>globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>cok lokasyonlu operasyon ve saha ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>Merhaba Onur, Sabanci Holding için Talent Management Specialist rolünüzü gördüm. Conglomerate tarafında globalleşme ve liderlik gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Onur, Getir icin Insan Kaynaklari Muduru rolunuzu gordum. Quick commerce / Delivery tarafinda cok lokasyonlu operasyon ve saha ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'cok lokasyonlu operasyon ve saha ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L7" t="str">
-        <x:v>Subject: Sabanci Holding ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Getir ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Onur,
-Sabanci Holding ekibinin Conglomerate ölçeğinde globalleşme ve liderlik gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Sabanci Holding için mantıklı pilot segmentini birlikte çıkaralım.
+Getir ekibinin Quick commerce / Delivery olceginde cok lokasyonlu operasyon ve saha ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: cok lokasyonlu operasyon ve saha ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Getir icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -493,268 +493,268 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>Mehmet Celik</x:v>
+        <x:v>Selin Aydin</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Tofas</x:v>
+        <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D8" t="str"/>
       <x:c r="E8" t="str"/>
       <x:c r="F8" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G8" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H8" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I8" t="str">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>Merhaba Mehmet, Tofas için HR Business Partner rolünüzü gördüm. Automotive / Manufacturing tarafında mavi yaka, beyaz yaka ve global partner dengesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Mavi icin Insan Kaynaklari Uzmani rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>Subject: Tofas ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Tofas ekibinin Automotive / Manufacturing ölçeğinde mavi yaka, beyaz yaka ve global partner dengesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Tofas için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>Kerem Polat</x:v>
+        <x:v>Ceren Koc</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>Trendyol</x:v>
+        <x:v>Arcelik</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D9" t="str"/>
       <x:c r="E9" t="str"/>
       <x:c r="F9" t="str">
-        <x:v>E-commerce / Marketplace</x:v>
+        <x:v>Consumer durables / Manufacturing</x:v>
       </x:c>
       <x:c r="G9" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H9" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>Merhaba Kerem, Trendyol için People and Culture Manager rolünüzü gördüm. E-commerce / Marketplace tarafında hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Arcelik icin HR Business Partner rolunuzu gordum. Consumer durables / Manufacturing tarafinda global marka ve cok ulkeli ekip yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>Subject: Trendyol ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Kerem,
-Trendyol ekibinin E-commerce / Marketplace ölçeğinde hızlı ölçeklenen ekipler ve uluslararası operasyon odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Trendyol için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Arcelik ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Arcelik ekibinin Consumer durables / Manufacturing olceginde global marka ve cok ulkeli ekip yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Arcelik icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>Mert Demir</x:v>
+        <x:v>Berk Koc</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>Colendi</x:v>
+        <x:v>Sabanci Holding</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D10" t="str"/>
       <x:c r="E10" t="str"/>
       <x:c r="F10" t="str">
-        <x:v>Fintech</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H10" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I10" t="str">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>Merhaba Mert, Colendi için People and Culture Manager rolünüzü gördüm. Fintech tarafında uluslararası fintech ürünleşmesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Sabanci Holding icin Human Resources Director rolunuzu gordum. Conglomerate tarafinda globallesme ve liderlik gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>Subject: Colendi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mert,
-Colendi ekibinin Fintech ölçeğinde uluslararası fintech ürünleşmesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Colendi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Sabanci Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Sabanci Holding ekibinin Conglomerate olceginde globallesme ve liderlik gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Sabanci Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>Selin Sahin</x:v>
+        <x:v>Onur Bulut</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>Peak Games</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D11" t="str"/>
       <x:c r="E11" t="str"/>
       <x:c r="F11" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H11" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>Merhaba Selin, Peak Games için People and Culture Manager rolünüzü gördüm. Gaming / Technology tarafında global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Onur, Garanti BBVA icin Talent Acquisition Manager rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Subject: Peak Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Selin,
-Peak Games ekibinin Gaming / Technology ölçeğinde global ürün ve çok uluslu çalışma ritmi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Peak Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Onur,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>Gizem Aslan</x:v>
+        <x:v>Deniz Kaya</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Yapi Kredi</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D12" t="str"/>
       <x:c r="E12" t="str"/>
       <x:c r="F12" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H12" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>Merhaba Gizem, Yemeksepeti için Talent Management Specialist rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Deniz, Yapi Kredi icin Insan Kaynaklari Uzmani rolunuzu gordum. Banking / Finance tarafinda sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Gizem,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yapi Kredi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Deniz,
+Yapi Kredi ekibinin Banking / Finance olceginde sube, merkez ve teknoloji ekiplerinin karma yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yapi Kredi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>Onur Polat</x:v>
+        <x:v>Emre Acar</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>LC Waikiki</x:v>
+        <x:v>Logo Yazilim</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D13" t="str"/>
       <x:c r="E13" t="str"/>
       <x:c r="F13" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>B2B SaaS / Software</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H13" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>73</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Merhaba Onur, LC Waikiki için People and Culture Manager rolünüzü gördüm. Retail / Fashion tarafında mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Emre, Logo Yazilim icin Talent Acquisition Manager rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Subject: LC Waikiki ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-LC Waikiki ekibinin Retail / Fashion ölçeğinde mağaza, merkez ve yurt dışı perakende operasyonları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede LC Waikiki için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Emre,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>77</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>Irem Acar</x:v>
+        <x:v>Mehmet Sahin</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C14" t="str">
         <x:v>HR Business Partner</x:v>
@@ -762,389 +762,389 @@
       <x:c r="D14" t="str"/>
       <x:c r="E14" t="str"/>
       <x:c r="F14" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H14" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Merhaba Irem, Mavi için HR Business Partner rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mehmet, Koc Holding icin HR Business Partner rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Irem,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mehmet,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>71</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>Irem Arslan</x:v>
+        <x:v>Tolga Aslan</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>Arcelik</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D15" t="str"/>
       <x:c r="E15" t="str"/>
       <x:c r="F15" t="str">
-        <x:v>Consumer durables / Manufacturing</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G15" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H15" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Merhaba Irem, Arcelik için Talent Acquisition Manager rolünüzü gördüm. Consumer durables / Manufacturing tarafında global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Isbank icin Insan Kaynaklari Uzmani rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L15" t="str">
-        <x:v>Subject: Arcelik ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Irem,
-Arcelik ekibinin Consumer durables / Manufacturing ölçeğinde global marka ve çok ülkeli ekip yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Arcelik için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>Deniz Polat</x:v>
+        <x:v>Ceren Koc</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>Sabanci Holding</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D16" t="str"/>
       <x:c r="E16" t="str"/>
       <x:c r="F16" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H16" t="str">
-        <x:v>globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>Merhaba Deniz, Sabanci Holding için Human Resources Director rolünüzü gördüm. Conglomerate tarafında globalleşme ve liderlik gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Colendi icin Organizational Development Manager rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>Subject: Sabanci Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Deniz,
-Sabanci Holding ekibinin Conglomerate ölçeğinde globalleşme ve liderlik gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Globalleşme ve liderlik gelişimi nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Sabanci Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>Onur Yilmaz</x:v>
+        <x:v>Kerem Bulut</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D17" t="str"/>
       <x:c r="E17" t="str"/>
       <x:c r="F17" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H17" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>Merhaba Onur, Yemeksepeti için Employee Experience Lead rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Koc Holding icin Talent Management Specialist rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>Derya Yilmaz</x:v>
+        <x:v>Ece Aslan</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D18" t="str"/>
       <x:c r="E18" t="str"/>
       <x:c r="F18" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H18" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>Merhaba Derya, Mavi için Talent Acquisition Manager rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ece, Koc Holding icin Learning and Development Manager rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Derya,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ece,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>Burak Aydin</x:v>
+        <x:v>Ece Kaya</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>Insider</x:v>
+        <x:v>Trendyol</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D19" t="str"/>
       <x:c r="E19" t="str"/>
       <x:c r="F19" t="str">
-        <x:v>B2B SaaS / MarTech</x:v>
+        <x:v>E-commerce / Marketplace</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H19" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>Merhaba Burak, Insider için Learning and Development Manager rolünüzü gördüm. B2B SaaS / MarTech tarafında global SaaS satış, müşteri başarısı ve ürün ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ece, Trendyol icin HR Business Partner rolunuzu gordum. E-commerce / Marketplace tarafinda hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>Subject: Insider ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Insider ekibinin B2B SaaS / MarTech ölçeğinde global SaaS satış, müşteri başarısı ve ürün ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Insider için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Trendyol ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ece,
+Trendyol ekibinin E-commerce / Marketplace olceginde hizli olceklenen ekipler ve uluslararasi operasyon odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Trendyol icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>Emre Erdem</x:v>
+        <x:v>Tolga Sahin</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Dream Games</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D20" t="str"/>
       <x:c r="E20" t="str"/>
       <x:c r="F20" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H20" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Merhaba Emre, Yapi Kredi için Organizational Development Manager rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Dream Games icin Learning and Development Manager rolunuzu gordum. Gaming / Technology tarafinda global urun ekipleri ve hizli ise alim nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Dream Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Dream Games ekibinin Gaming / Technology olceginde global urun ekipleri ve hizli ise alim odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Dream Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>Elif Sahin</x:v>
+        <x:v>Ceren Sahin</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>Turkcell</x:v>
+        <x:v>Logo Yazilim</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D21" t="str"/>
       <x:c r="E21" t="str"/>
       <x:c r="F21" t="str">
-        <x:v>Telecommunications</x:v>
+        <x:v>B2B SaaS / Software</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H21" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Merhaba Elif, Turkcell için HR Business Partner rolünüzü gördüm. Telecommunications tarafında kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Logo Yazilim icin Insan Kaynaklari Uzmani rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>Subject: Turkcell ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-Turkcell ekibinin Telecommunications ölçeğinde kurumsal dönüşüm ve teknoloji yetkinlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Turkcell için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>Emre Celik</x:v>
+        <x:v>Kerem Kaplan</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D22" t="str"/>
       <x:c r="E22" t="str"/>
       <x:c r="F22" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G22" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Merhaba Emre, Ford Otosan için Talent Management Specialist rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Koc Holding icin Organizational Development Manager rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>78</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>Zeynep Koc</x:v>
+        <x:v>Kerem Aslan</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Tofas</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D23" t="str"/>
       <x:c r="E23" t="str"/>
@@ -1155,23 +1155,23 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Merhaba Zeynep, Ford Otosan için HR Business Partner rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Tofas icin Employee Experience Lead rolunuzu gordum. Automotive / Manufacturing tarafinda mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Tofas ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Tofas ekibinin Automotive / Manufacturing olceginde mavi yaka, beyaz yaka ve global partner dengesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Tofas icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -1181,13 +1181,13 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>Onur Sahin</x:v>
+        <x:v>Derya Polat</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D24" t="str"/>
       <x:c r="E24" t="str"/>
@@ -1198,125 +1198,125 @@
         <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I24" t="str">
         <x:v>70</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Merhaba Onur, Mavi için Talent Management Specialist rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Mavi icin Organizational Development Manager rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>Ayse Aslan</x:v>
+        <x:v>Burak Acar</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>Logo Yazilim</x:v>
+        <x:v>Ford Otosan</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D25" t="str"/>
       <x:c r="E25" t="str"/>
       <x:c r="F25" t="str">
-        <x:v>B2B SaaS / Software</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>Merhaba Ayse, Logo Yazilim için Employee Experience Lead rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Burak, Ford Otosan icin HR Business Partner rolunuzu gordum. Automotive / Manufacturing tarafinda uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ayse,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Ford Otosan ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Burak,
+Ford Otosan ekibinin Automotive / Manufacturing olceginde uretim, muhendislik ve global tedarik zinciri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Ford Otosan icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>Ayse Polat</x:v>
+        <x:v>Kerem Aydin</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>Akbank</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D26" t="str"/>
       <x:c r="E26" t="str"/>
       <x:c r="F26" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Merhaba Ayse, Akbank için Human Resources Director rolünüzü gördüm. Banking / Finance tarafında dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Colendi icin Learning and Development Manager rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Subject: Akbank ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ayse,
-Akbank ekibinin Banking / Finance ölçeğinde dijital bankacılık ve yetenek dönüşümü odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Akbank için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>Emre Demir</x:v>
+        <x:v>Elif Arslan</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>Colendi</x:v>
+        <x:v>Papara</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D27" t="str"/>
       <x:c r="E27" t="str"/>
@@ -1327,168 +1327,168 @@
         <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>Merhaba Emre, Colendi için Learning and Development Manager rolünüzü gördüm. Fintech tarafında uluslararası fintech ürünleşmesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Papara icin Organizational Development Manager rolunuzu gordum. Fintech tarafinda fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Subject: Colendi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Colendi ekibinin Fintech ölçeğinde uluslararası fintech ürünleşmesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Colendi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Papara ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Papara ekibinin Fintech olceginde fintech buyumesi ve regulasyonla uyumlu ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Papara icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>Onur Ozdemir</x:v>
+        <x:v>Ceren Demir</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D28" t="str"/>
       <x:c r="E28" t="str"/>
       <x:c r="F28" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Merhaba Onur, Mavi için People and Culture Manager rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Colendi icin Employee Experience Lead rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>73</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>Onur Kaplan</x:v>
+        <x:v>Derya Erdem</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Peak Games</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D29" t="str"/>
       <x:c r="E29" t="str"/>
       <x:c r="F29" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>global urun ve cok uluslu calisma ritmi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>76</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Merhaba Onur, Yemeksepeti için Human Resources Director rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Peak Games icin Insan Kaynaklari Muduru rolunuzu gordum. Gaming / Technology tarafinda global urun ve cok uluslu calisma ritmi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global urun ve cok uluslu calisma ritmi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Peak Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Peak Games ekibinin Gaming / Technology olceginde global urun ve cok uluslu calisma ritmi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global urun ve cok uluslu calisma ritmi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Peak Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>Zeynep Sahin</x:v>
+        <x:v>Elif Kara</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>Hepsiburada</x:v>
+        <x:v>Insider</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D30" t="str"/>
       <x:c r="E30" t="str"/>
       <x:c r="F30" t="str">
-        <x:v>E-commerce / Retail tech</x:v>
+        <x:v>B2B SaaS / MarTech</x:v>
       </x:c>
       <x:c r="G30" t="str">
         <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H30" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>80</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Merhaba Zeynep, Hepsiburada için Learning and Development Manager rolünüzü gördüm. E-commerce / Retail tech tarafında müşteri deneyimi ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Insider icin Insan Kaynaklari Muduru rolunuzu gordum. B2B SaaS / MarTech tarafinda global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Subject: Hepsiburada ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Hepsiburada ekibinin E-commerce / Retail tech ölçeğinde müşteri deneyimi ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Hepsiburada için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Insider ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Insider ekibinin B2B SaaS / MarTech olceginde global SaaS satis, musteri basarisi ve urun ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Insider icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M30" t="str">
-        <x:v>83</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>Emre Aslan</x:v>
+        <x:v>Irem Yilmaz</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>Turkcell</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D31" t="str"/>
       <x:c r="E31" t="str"/>
@@ -1499,294 +1499,294 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I31" t="str">
         <x:v>84</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Merhaba Emre, Turkcell için Human Resources Director rolünüzü gördüm. Telecommunications tarafında kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Irem, Turkcell icin HR Business Partner rolunuzu gordum. Telecommunications tarafinda kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Subject: Turkcell ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Turkcell ekibinin Telecommunications ölçeğinde kurumsal dönüşüm ve teknoloji yetkinlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Turkcell için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Turkcell ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Irem,
+Turkcell ekibinin Telecommunications olceginde kurumsal donusum ve teknoloji yetkinlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Turkcell icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>Ece Kilic</x:v>
+        <x:v>Derya Acar</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>Vestel</x:v>
+        <x:v>Logo Yazilim</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D32" t="str"/>
       <x:c r="E32" t="str"/>
       <x:c r="F32" t="str">
-        <x:v>Electronics / Manufacturing</x:v>
+        <x:v>B2B SaaS / Software</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H32" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>79</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>Merhaba Ece, Vestel için HR Business Partner rolünüzü gördüm. Electronics / Manufacturing tarafında ihracat ağı ve teknik ekiplerin İngilizce ihtiyacı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Logo Yazilim icin Insan Kaynaklari Uzmani rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Subject: Vestel ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ece,
-Vestel ekibinin Electronics / Manufacturing ölçeğinde ihracat ağı ve teknik ekiplerin İngilizce ihtiyacı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Vestel için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>Zeynep Demir</x:v>
+        <x:v>Gizem Yildiz</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>Papara</x:v>
+        <x:v>Insider</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D33" t="str"/>
       <x:c r="E33" t="str"/>
       <x:c r="F33" t="str">
-        <x:v>Fintech</x:v>
+        <x:v>B2B SaaS / MarTech</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H33" t="str">
-        <x:v>fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>Merhaba Zeynep, Papara için Human Resources Director rolünüzü gördüm. Fintech tarafında fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Insider icin People and Culture Manager rolunuzu gordum. B2B SaaS / MarTech tarafinda global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>Subject: Papara ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Papara ekibinin Fintech ölçeğinde fintech büyümesi ve regülasyonla uyumlu ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Papara için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Insider ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Insider ekibinin B2B SaaS / MarTech olceginde global SaaS satis, musteri basarisi ve urun ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Insider icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M33" t="str">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>Tolga Acar</x:v>
+        <x:v>Mert Demir</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>Garanti BBVA</x:v>
+        <x:v>LC Waikiki</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D34" t="str"/>
       <x:c r="E34" t="str"/>
       <x:c r="F34" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G34" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H34" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>magaza, merkez ve yurt disi perakende operasyonlari nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Merhaba Tolga, Garanti BBVA için Organizational Development Manager rolünüzü gördüm. Banking / Finance tarafında global bankacılık standartları ve dijitalleşme nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, LC Waikiki icin Talent Management Specialist rolunuzu gordum. Retail / Fashion tarafinda magaza, merkez ve yurt disi perakende operasyonlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'magaza, merkez ve yurt disi perakende operasyonlari nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Subject: Garanti BBVA ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Tolga,
-Garanti BBVA ekibinin Banking / Finance ölçeğinde global bankacılık standartları ve dijitalleşme odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Garanti BBVA için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: LC Waikiki ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mert,
+LC Waikiki ekibinin Retail / Fashion olceginde magaza, merkez ve yurt disi perakende operasyonlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: magaza, merkez ve yurt disi perakende operasyonlari nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede LC Waikiki icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>90</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>Zeynep Kaya</x:v>
+        <x:v>Elif Celik</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Dream Games</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D35" t="str"/>
       <x:c r="E35" t="str"/>
       <x:c r="F35" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H35" t="str">
-        <x:v>perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>70</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Merhaba Zeynep, Mavi için Human Resources Director rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Dream Games icin Learning and Development Manager rolunuzu gordum. Gaming / Technology tarafinda global urun ekipleri ve hizli ise alim nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Dream Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Dream Games ekibinin Gaming / Technology olceginde global urun ekipleri ve hizli ise alim odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Dream Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M35" t="str">
-        <x:v>75</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>Burak Erdem</x:v>
+        <x:v>Berk Demir</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D36" t="str"/>
       <x:c r="E36" t="str"/>
       <x:c r="F36" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G36" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H36" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Merhaba Burak, Yapi Kredi için People and Culture Manager rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Koc Holding icin Human Resources Director rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M36" t="str">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>Onur Aslan</x:v>
+        <x:v>Mert Koc</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>Arcelik</x:v>
+        <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D37" t="str"/>
       <x:c r="E37" t="str"/>
       <x:c r="F37" t="str">
-        <x:v>Consumer durables / Manufacturing</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G37" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H37" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Merhaba Onur, Arcelik için People and Culture Manager rolünüzü gördüm. Consumer durables / Manufacturing tarafında global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, Koc Holding icin Employee Experience Lead rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Subject: Arcelik ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Arcelik ekibinin Consumer durables / Manufacturing ölçeğinde global marka ve çok ülkeli ekip yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Arcelik için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mert,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>Elif Celik</x:v>
+        <x:v>Gizem Polat</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>Arcelik</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C38" t="str">
         <x:v>Employee Experience Lead</x:v>
@@ -1794,45 +1794,45 @@
       <x:c r="D38" t="str"/>
       <x:c r="E38" t="str"/>
       <x:c r="F38" t="str">
-        <x:v>Consumer durables / Manufacturing</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H38" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Merhaba Elif, Arcelik için Employee Experience Lead rolünüzü gördüm. Consumer durables / Manufacturing tarafında global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Colendi icin Employee Experience Lead rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Subject: Arcelik ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-Arcelik ekibinin Consumer durables / Manufacturing ölçeğinde global marka ve çok ülkeli ekip yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Arcelik için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>Burak Koc</x:v>
+        <x:v>Derya Acar</x:v>
       </x:c>
       <x:c r="B39" t="str">
         <x:v>Yapi Kredi</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D39" t="str"/>
       <x:c r="E39" t="str"/>
@@ -1843,23 +1843,23 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H39" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>82</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>Merhaba Burak, Yapi Kredi için Talent Acquisition Manager rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Yapi Kredi icin People and Culture Manager rolunuzu gordum. Banking / Finance tarafinda sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yapi Kredi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Yapi Kredi ekibinin Banking / Finance olceginde sube, merkez ve teknoloji ekiplerinin karma yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yapi Kredi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -1869,96 +1869,96 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>Kerem Ozturk</x:v>
+        <x:v>Mert Erdem</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>Logo Yazilim</x:v>
+        <x:v>Ford Otosan</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D40" t="str"/>
       <x:c r="E40" t="str"/>
       <x:c r="F40" t="str">
-        <x:v>B2B SaaS / Software</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H40" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>Merhaba Kerem, Logo Yazilim için Talent Acquisition Manager rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, Ford Otosan icin Insan Kaynaklari Muduru rolunuzu gordum. Automotive / Manufacturing tarafinda uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Kerem,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Ford Otosan ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mert,
+Ford Otosan ekibinin Automotive / Manufacturing olceginde uretim, muhendislik ve global tedarik zinciri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Ford Otosan icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M40" t="str">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>Selin Arslan</x:v>
+        <x:v>Ayse Cetin</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>LC Waikiki</x:v>
+        <x:v>Peak Games</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D41" t="str"/>
       <x:c r="E41" t="str"/>
       <x:c r="F41" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H41" t="str">
-        <x:v>mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>Merhaba Selin, LC Waikiki için Human Resources Director rolünüzü gördüm. Retail / Fashion tarafında mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ayse, Peak Games icin HR Business Partner rolunuzu gordum. Gaming / Technology tarafinda global urun ve cok uluslu calisma ritmi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Subject: LC Waikiki ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Selin,
-LC Waikiki ekibinin Retail / Fashion ölçeğinde mağaza, merkez ve yurt dışı perakende operasyonları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede LC Waikiki için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Peak Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ayse,
+Peak Games ekibinin Gaming / Technology olceginde global urun ve cok uluslu calisma ritmi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Peak Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>79</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>Zeynep Arslan</x:v>
+        <x:v>Tolga Celik</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>LC Waikiki</x:v>
+        <x:v>Eczacibasi</x:v>
       </x:c>
       <x:c r="C42" t="str">
         <x:v>HR Business Partner</x:v>
@@ -1966,158 +1966,158 @@
       <x:c r="D42" t="str"/>
       <x:c r="E42" t="str"/>
       <x:c r="F42" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Conglomerate / Healthcare / Industry</x:v>
       </x:c>
       <x:c r="G42" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H42" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>Merhaba Zeynep, LC Waikiki için HR Business Partner rolünüzü gördüm. Retail / Fashion tarafında mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Eczacibasi icin HR Business Partner rolunuzu gordum. Conglomerate / Healthcare / Industry tarafinda cok sektorlu yetenek gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>Subject: LC Waikiki ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-LC Waikiki ekibinin Retail / Fashion ölçeğinde mağaza, merkez ve yurt dışı perakende operasyonları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede LC Waikiki için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Eczacibasi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Eczacibasi ekibinin Conglomerate / Healthcare / Industry olceginde cok sektorlu yetenek gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Eczacibasi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M42" t="str">
-        <x:v>75</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>Burak Demir</x:v>
+        <x:v>Asli Acar</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Yapi Kredi</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D43" t="str"/>
       <x:c r="E43" t="str"/>
       <x:c r="F43" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H43" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>Merhaba Burak, Yemeksepeti için Learning and Development Manager rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Asli, Yapi Kredi icin Organizational Development Manager rolunuzu gordum. Banking / Finance tarafinda sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yapi Kredi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Asli,
+Yapi Kredi ekibinin Banking / Finance olceginde sube, merkez ve teknoloji ekiplerinin karma yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yapi Kredi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M43" t="str">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>Emre Yilmaz</x:v>
+        <x:v>Berk Acar</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>Getir</x:v>
+        <x:v>Dream Games</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D44" t="str"/>
       <x:c r="E44" t="str"/>
       <x:c r="F44" t="str">
-        <x:v>Quick commerce / Delivery</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G44" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H44" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J44" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>Merhaba Emre, Getir için Organizational Development Manager rolünüzü gördüm. Quick commerce / Delivery tarafında çok lokasyonlu operasyon ve saha ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Dream Games icin Insan Kaynaklari Muduru rolunuzu gordum. Gaming / Technology tarafinda global urun ekipleri ve hizli ise alim nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>Subject: Getir ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Getir ekibinin Quick commerce / Delivery ölçeğinde çok lokasyonlu operasyon ve saha ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Getir için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Dream Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Dream Games ekibinin Gaming / Technology olceginde global urun ekipleri ve hizli ise alim odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Dream Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M44" t="str">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>Can Kara</x:v>
+        <x:v>Tolga Bulut</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>Akbank</x:v>
+        <x:v>Turkcell</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D45" t="str"/>
       <x:c r="E45" t="str"/>
       <x:c r="F45" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Telecommunications</x:v>
       </x:c>
       <x:c r="G45" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H45" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>Merhaba Can, Akbank için Learning and Development Manager rolünüzü gördüm. Banking / Finance tarafında dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Turkcell icin Insan Kaynaklari Uzmani rolunuzu gordum. Telecommunications tarafinda kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>Subject: Akbank ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Akbank ekibinin Banking / Finance ölçeğinde dijital bankacılık ve yetenek dönüşümü odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Akbank için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Turkcell ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Turkcell ekibinin Telecommunications olceginde kurumsal donusum ve teknoloji yetkinlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Turkcell icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -2127,10 +2127,10 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>Can Aydin</x:v>
+        <x:v>Ece Kaplan</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>Logo Yazilim</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C46" t="str">
         <x:v>Talent Management Specialist</x:v>
@@ -2138,287 +2138,287 @@
       <x:c r="D46" t="str"/>
       <x:c r="E46" t="str"/>
       <x:c r="F46" t="str">
-        <x:v>B2B SaaS / Software</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G46" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H46" t="str">
-        <x:v>teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>Merhaba Can, Logo Yazilim için Talent Management Specialist rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ece, Colendi icin Talent Management Specialist rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ece,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M46" t="str">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>Mehmet Sahin</x:v>
+        <x:v>Tolga Kaya</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>Turkcell</x:v>
+        <x:v>Yemeksepeti</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D47" t="str"/>
       <x:c r="E47" t="str"/>
       <x:c r="F47" t="str">
-        <x:v>Telecommunications</x:v>
+        <x:v>Food delivery / Tech</x:v>
       </x:c>
       <x:c r="G47" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H47" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J47" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>Merhaba Mehmet, Turkcell için Organizational Development Manager rolünüzü gördüm. Telecommunications tarafında kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Yemeksepeti icin Employee Experience Lead rolunuzu gordum. Food delivery / Tech tarafinda operasyon, satis ve teknoloji ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L47" t="str">
-        <x:v>Subject: Turkcell ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Turkcell ekibinin Telecommunications ölçeğinde kurumsal dönüşüm ve teknoloji yetkinlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Turkcell için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yemeksepeti ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Yemeksepeti ekibinin Food delivery / Tech olceginde operasyon, satis ve teknoloji ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yemeksepeti icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M47" t="str">
-        <x:v>91</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>Can Demir</x:v>
+        <x:v>Ayse Demir</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Tofas</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D48" t="str"/>
       <x:c r="E48" t="str"/>
       <x:c r="F48" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G48" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H48" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>92</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>Merhaba Can, Dream Games için Talent Acquisition Manager rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ayse, Tofas icin Talent Management Specialist rolunuzu gordum. Automotive / Manufacturing tarafinda mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Tofas ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ayse,
+Tofas ekibinin Automotive / Manufacturing olceginde mavi yaka, beyaz yaka ve global partner dengesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Tofas icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M48" t="str">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>Deniz Aslan</x:v>
+        <x:v>Gizem Kaya</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>Logo Yazilim</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D49" t="str"/>
       <x:c r="E49" t="str"/>
       <x:c r="F49" t="str">
-        <x:v>B2B SaaS / Software</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G49" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H49" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J49" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>Merhaba Deniz, Logo Yazilim için HR Business Partner rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Colendi icin Talent Management Specialist rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Deniz,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M49" t="str">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>Mehmet Yildiz</x:v>
+        <x:v>Derya Arslan</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>Vodafone Turkey</x:v>
+        <x:v>Hepsiburada</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D50" t="str"/>
       <x:c r="E50" t="str"/>
       <x:c r="F50" t="str">
-        <x:v>Telecommunications</x:v>
+        <x:v>E-commerce / Retail tech</x:v>
       </x:c>
       <x:c r="G50" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H50" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>Merhaba Mehmet, Vodafone Turkey için Organizational Development Manager rolünüzü gördüm. Telecommunications tarafında global ekiplerle yoğun iş birliği nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Hepsiburada icin Employee Experience Lead rolunuzu gordum. E-commerce / Retail tech tarafinda musteri deneyimi ve teknoloji ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>Subject: Vodafone Turkey ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Vodafone Turkey ekibinin Telecommunications ölçeğinde global ekiplerle yoğun iş birliği odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Vodafone Turkey için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Hepsiburada ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Hepsiburada ekibinin E-commerce / Retail tech olceginde musteri deneyimi ve teknoloji ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Hepsiburada icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M50" t="str">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>Ceren Arslan</x:v>
+        <x:v>Ceren Aslan</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D51" t="str"/>
       <x:c r="E51" t="str"/>
       <x:c r="F51" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G51" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H51" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>Merhaba Ceren, Yemeksepeti için Human Resources Director rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Isbank icin Learning and Development Manager rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L51" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Ceren,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M51" t="str">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>Kerem Bulut</x:v>
+        <x:v>Gizem Polat</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>Koc Holding</x:v>
+        <x:v>Turkcell</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D52" t="str"/>
       <x:c r="E52" t="str"/>
       <x:c r="F52" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>Telecommunications</x:v>
       </x:c>
       <x:c r="G52" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H52" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>Merhaba Kerem, Koc Holding için Learning and Development Manager rolünüzü gördüm. Conglomerate tarafında grup şirketleri arası ortak gelişim programları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Turkcell icin Insan Kaynaklari Muduru rolunuzu gordum. Telecommunications tarafinda kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L52" t="str">
-        <x:v>Subject: Koc Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Kerem,
-Koc Holding ekibinin Conglomerate ölçeğinde grup şirketleri arası ortak gelişim programları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Koc Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Turkcell ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Turkcell ekibinin Telecommunications olceginde kurumsal donusum ve teknoloji yetkinlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Turkcell icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -2428,99 +2428,99 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>Elif Yilmaz</x:v>
+        <x:v>Selin Aydin</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>Sabanci Holding</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D53" t="str"/>
       <x:c r="E53" t="str"/>
       <x:c r="F53" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G53" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H53" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J53" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>Merhaba Elif, Sabanci Holding için HR Business Partner rolünüzü gördüm. Conglomerate tarafında globalleşme ve liderlik gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Colendi icin Human Resources Director rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>Subject: Sabanci Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-Sabanci Holding ekibinin Conglomerate ölçeğinde globalleşme ve liderlik gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Sabanci Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M53" t="str">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>Burak Cetin</x:v>
+        <x:v>Kerem Celik</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>Getir</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D54" t="str"/>
       <x:c r="E54" t="str"/>
       <x:c r="F54" t="str">
-        <x:v>Quick commerce / Delivery</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G54" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H54" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J54" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>Merhaba Burak, Getir için Employee Experience Lead rolünüzü gördüm. Quick commerce / Delivery tarafında çok lokasyonlu operasyon ve saha ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Kerem, Colendi icin Insan Kaynaklari Muduru rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>Subject: Getir ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Getir ekibinin Quick commerce / Delivery ölçeğinde çok lokasyonlu operasyon ve saha ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Getir için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Kerem,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M54" t="str">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>Irem Bulut</x:v>
+        <x:v>Selin Yilmaz</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>Akbank</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D55" t="str"/>
       <x:c r="E55" t="str"/>
@@ -2531,36 +2531,36 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H55" t="str">
-        <x:v>dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>Merhaba Irem, Akbank için Talent Management Specialist rolünüzü gördüm. Banking / Finance tarafında dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Garanti BBVA icin People and Culture Manager rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>Subject: Akbank ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Irem,
-Akbank ekibinin Banking / Finance ölçeğinde dijital bankacılık ve yetenek dönüşümü odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Akbank için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M55" t="str">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>Tolga Ozturk</x:v>
+        <x:v>Elif Yilmaz</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>Logo Yazilim</x:v>
+        <x:v>Yapi Kredi</x:v>
       </x:c>
       <x:c r="C56" t="str">
         <x:v>Talent Acquisition Manager</x:v>
@@ -2568,211 +2568,211 @@
       <x:c r="D56" t="str"/>
       <x:c r="E56" t="str"/>
       <x:c r="F56" t="str">
-        <x:v>B2B SaaS / Software</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G56" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H56" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>Merhaba Tolga, Logo Yazilim için Talent Acquisition Manager rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Yapi Kredi icin Talent Acquisition Manager rolunuzu gordum. Banking / Finance tarafinda sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Tolga,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yapi Kredi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Yapi Kredi ekibinin Banking / Finance olceginde sube, merkez ve teknoloji ekiplerinin karma yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yapi Kredi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M56" t="str">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>Ayse Erdem</x:v>
+        <x:v>Elif Aydin</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>Peak Games</x:v>
+        <x:v>Sabanci Holding</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D57" t="str"/>
       <x:c r="E57" t="str"/>
       <x:c r="F57" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G57" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H57" t="str">
-        <x:v>global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>Merhaba Ayse, Peak Games için Talent Management Specialist rolünüzü gördüm. Gaming / Technology tarafında global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Sabanci Holding icin Insan Kaynaklari Muduru rolunuzu gordum. Conglomerate tarafinda globallesme ve liderlik gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L57" t="str">
-        <x:v>Subject: Peak Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ayse,
-Peak Games ekibinin Gaming / Technology ölçeğinde global ürün ve çok uluslu çalışma ritmi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Peak Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Sabanci Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Sabanci Holding ekibinin Conglomerate olceginde globallesme ve liderlik gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Sabanci Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M57" t="str">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>Tolga Aydin</x:v>
+        <x:v>Tolga Arslan</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Eczacibasi</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D58" t="str"/>
       <x:c r="E58" t="str"/>
       <x:c r="F58" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Conglomerate / Healthcare / Industry</x:v>
       </x:c>
       <x:c r="G58" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H58" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J58" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>Merhaba Tolga, Yapi Kredi için Talent Acquisition Manager rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Eczacibasi icin Employee Experience Lead rolunuzu gordum. Conglomerate / Healthcare / Industry tarafinda cok sektorlu yetenek gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L58" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Eczacibasi ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Tolga,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+Eczacibasi ekibinin Conglomerate / Healthcare / Industry olceginde cok sektorlu yetenek gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Eczacibasi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M58" t="str">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>Ayse Polat</x:v>
+        <x:v>Can Cetin</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>Tofas</x:v>
+        <x:v>Yemeksepeti</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D59" t="str"/>
       <x:c r="E59" t="str"/>
       <x:c r="F59" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Food delivery / Tech</x:v>
       </x:c>
       <x:c r="G59" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H59" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>Merhaba Ayse, Tofas için Learning and Development Manager rolünüzü gördüm. Automotive / Manufacturing tarafında mavi yaka, beyaz yaka ve global partner dengesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Can, Yemeksepeti icin Employee Experience Lead rolunuzu gordum. Food delivery / Tech tarafinda operasyon, satis ve teknoloji ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>Subject: Tofas ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ayse,
-Tofas ekibinin Automotive / Manufacturing ölçeğinde mavi yaka, beyaz yaka ve global partner dengesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Tofas için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yemeksepeti ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Can,
+Yemeksepeti ekibinin Food delivery / Tech olceginde operasyon, satis ve teknoloji ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yemeksepeti icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M59" t="str">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>Tolga Aydin</x:v>
+        <x:v>Selin Demir</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>Eczacibasi</x:v>
+        <x:v>Hepsiburada</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D60" t="str"/>
       <x:c r="E60" t="str"/>
       <x:c r="F60" t="str">
-        <x:v>Conglomerate / Healthcare / Industry</x:v>
+        <x:v>E-commerce / Retail tech</x:v>
       </x:c>
       <x:c r="G60" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H60" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>musteri deneyimi ve teknoloji ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>Merhaba Tolga, Eczacibasi için Learning and Development Manager rolünüzü gördüm. Conglomerate / Healthcare / Industry tarafında çok sektörlü yetenek gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Hepsiburada icin Human Resources Director rolunuzu gordum. E-commerce / Retail tech tarafinda musteri deneyimi ve teknoloji ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'musteri deneyimi ve teknoloji ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L60" t="str">
-        <x:v>Subject: Eczacibasi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Tolga,
-Eczacibasi ekibinin Conglomerate / Healthcare / Industry ölçeğinde çok sektörlü yetenek gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Eczacibasi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Hepsiburada ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Hepsiburada ekibinin E-commerce / Retail tech olceginde musteri deneyimi ve teknoloji ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: musteri deneyimi ve teknoloji ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Hepsiburada icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M60" t="str">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>Mehmet Kaya</x:v>
+        <x:v>Can Kara</x:v>
       </x:c>
       <x:c r="B61" t="str">
         <x:v>Logo Yazilim</x:v>
@@ -2789,23 +2789,23 @@
         <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H61" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I61" t="str">
         <x:v>85</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>Merhaba Mehmet, Logo Yazilim için Organizational Development Manager rolünüzü gördüm. B2B SaaS / Software tarafında teknoloji yetenekleri ve müşteri odaklı ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Can, Logo Yazilim icin Organizational Development Manager rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L61" t="str">
-        <x:v>Subject: Logo Yazilim ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Logo Yazilim ekibinin B2B SaaS / Software ölçeğinde teknoloji yetenekleri ve müşteri odaklı ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Logo Yazilim için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Can,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -2815,314 +2815,314 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>Can Ozdemir</x:v>
+        <x:v>Berk Celik</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Sabanci Holding</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>Learning and Development Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D62" t="str"/>
       <x:c r="E62" t="str"/>
       <x:c r="F62" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G62" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H62" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>76</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>Merhaba Can, Yemeksepeti için Learning and Development Manager rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Sabanci Holding icin Talent Acquisition Manager rolunuzu gordum. Conglomerate tarafinda globallesme ve liderlik gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Sabanci Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Sabanci Holding ekibinin Conglomerate olceginde globallesme ve liderlik gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Sabanci Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M62" t="str">
-        <x:v>79</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>Berk Ozturk</x:v>
+        <x:v>Elif Kara</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D63" t="str"/>
       <x:c r="E63" t="str"/>
       <x:c r="F63" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G63" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H63" t="str">
-        <x:v>global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J63" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>Merhaba Berk, Dream Games için Human Resources Director rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Garanti BBVA icin Insan Kaynaklari Uzmani rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L63" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Berk,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M63" t="str">
-        <x:v>100</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>Elif Arslan</x:v>
+        <x:v>Tolga Yildiz</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>LC Waikiki</x:v>
+        <x:v>Ford Otosan</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D64" t="str"/>
       <x:c r="E64" t="str"/>
       <x:c r="F64" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G64" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H64" t="str">
-        <x:v>mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>Merhaba Elif, LC Waikiki için Human Resources Director rolünüzü gördüm. Retail / Fashion tarafında mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Ford Otosan icin Insan Kaynaklari Uzmani rolunuzu gordum. Automotive / Manufacturing tarafinda uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L64" t="str">
-        <x:v>Subject: LC Waikiki ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-LC Waikiki ekibinin Retail / Fashion ölçeğinde mağaza, merkez ve yurt dışı perakende operasyonları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Mağaza, merkez ve yurt dışı perakende operasyonları nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede LC Waikiki için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Ford Otosan ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Ford Otosan ekibinin Automotive / Manufacturing olceginde uretim, muhendislik ve global tedarik zinciri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uretim, muhendislik ve global tedarik zinciri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Ford Otosan icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M64" t="str">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>Mert Koc</x:v>
+        <x:v>Can Ozturk</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>Garanti BBVA</x:v>
+        <x:v>Logo Yazilim</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D65" t="str"/>
       <x:c r="E65" t="str"/>
       <x:c r="F65" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>B2B SaaS / Software</x:v>
       </x:c>
       <x:c r="G65" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H65" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>Merhaba Mert, Garanti BBVA için Employee Experience Lead rolünüzü gördüm. Banking / Finance tarafında global bankacılık standartları ve dijitalleşme nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Can, Logo Yazilim icin Talent Acquisition Manager rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L65" t="str">
-        <x:v>Subject: Garanti BBVA ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mert,
-Garanti BBVA ekibinin Banking / Finance ölçeğinde global bankacılık standartları ve dijitalleşme odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Garanti BBVA için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Can,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M65" t="str">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>Ceren Kaplan</x:v>
+        <x:v>Ayse Polat</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Vestel</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D66" t="str"/>
       <x:c r="E66" t="str"/>
       <x:c r="F66" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Electronics / Manufacturing</x:v>
       </x:c>
       <x:c r="G66" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H66" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>92</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>Merhaba Ceren, Dream Games için Employee Experience Lead rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ayse, Vestel icin Learning and Development Manager rolunuzu gordum. Electronics / Manufacturing tarafinda ihracat agi ve teknik ekiplerin Ingilizce ihtiyaci nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L66" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ceren,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Vestel ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ayse,
+Vestel ekibinin Electronics / Manufacturing olceginde ihracat agi ve teknik ekiplerin Ingilizce ihtiyaci odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Vestel icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M66" t="str">
-        <x:v>97</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>Can Kara</x:v>
+        <x:v>Tolga Erdem</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>Akbank</x:v>
+        <x:v>Dream Games</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D67" t="str"/>
       <x:c r="E67" t="str"/>
       <x:c r="F67" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G67" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H67" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J67" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>Merhaba Can, Akbank için Organizational Development Manager rolünüzü gördüm. Banking / Finance tarafında dijital bankacılık ve yetenek dönüşümü nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Dream Games icin People and Culture Manager rolunuzu gordum. Gaming / Technology tarafinda global urun ekipleri ve hizli ise alim nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L67" t="str">
-        <x:v>Subject: Akbank ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Akbank ekibinin Banking / Finance ölçeğinde dijital bankacılık ve yetenek dönüşümü odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Akbank için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Dream Games ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Dream Games ekibinin Gaming / Technology olceginde global urun ekipleri ve hizli ise alim odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Dream Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M67" t="str">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>Ayse Ozturk</x:v>
+        <x:v>Ayse Kara</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Tofas</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D68" t="str"/>
       <x:c r="E68" t="str"/>
       <x:c r="F68" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G68" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H68" t="str">
-        <x:v>perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>Merhaba Ayse, Mavi için Human Resources Director rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ayse, Tofas icin People and Culture Manager rolunuzu gordum. Automotive / Manufacturing tarafinda mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Tofas ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Ayse,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+Tofas ekibinin Automotive / Manufacturing olceginde mavi yaka, beyaz yaka ve global partner dengesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Tofas icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M68" t="str">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>Tolga Yildiz</x:v>
+        <x:v>Selin Arslan</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>Isbank</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D69" t="str"/>
       <x:c r="E69" t="str"/>
@@ -3133,125 +3133,125 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H69" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>Merhaba Tolga, Isbank için HR Business Partner rolünüzü gördüm. Banking / Finance tarafında kurumsal ölçekte eğitim standardizasyonu nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Garanti BBVA icin Employee Experience Lead rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L69" t="str">
-        <x:v>Subject: Isbank ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Tolga,
-Isbank ekibinin Banking / Finance ölçeğinde kurumsal ölçekte eğitim standardizasyonu odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Isbank için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M69" t="str">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>Tolga Aslan</x:v>
+        <x:v>Tolga Koc</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>Colendi</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D70" t="str"/>
       <x:c r="E70" t="str"/>
       <x:c r="F70" t="str">
-        <x:v>Fintech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G70" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H70" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J70" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>Merhaba Tolga, Colendi için Employee Experience Lead rolünüzü gördüm. Fintech tarafında uluslararası fintech ürünleşmesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Isbank icin HR Business Partner rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L70" t="str">
-        <x:v>Subject: Colendi ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Tolga,
-Colendi ekibinin Fintech ölçeğinde uluslararası fintech ürünleşmesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Colendi için mantıklı pilot segmentini birlikte çıkaralım.
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M70" t="str">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>Emre Bulut</x:v>
+        <x:v>Elif Yildiz</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Sabanci Holding</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>Employee Experience Lead</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D71" t="str"/>
       <x:c r="E71" t="str"/>
       <x:c r="F71" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H71" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>Merhaba Emre, Dream Games için Employee Experience Lead rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Sabanci Holding icin Insan Kaynaklari Muduru rolunuzu gordum. Conglomerate tarafinda globallesme ve liderlik gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L71" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Sabanci Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Sabanci Holding ekibinin Conglomerate olceginde globallesme ve liderlik gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Sabanci Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M71" t="str">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>Tolga Kilic</x:v>
+        <x:v>Asli Sahin</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>Vodafone Turkey</x:v>
+        <x:v>Turkcell</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D72" t="str"/>
       <x:c r="E72" t="str"/>
@@ -3262,251 +3262,251 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H72" t="str">
-        <x:v>global ekiplerle yoğun iş birliği nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>Merhaba Tolga, Vodafone Turkey için Human Resources Director rolünüzü gördüm. Telecommunications tarafında global ekiplerle yoğun iş birliği nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Global ekiplerle yoğun iş birliği nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Asli, Turkcell icin People and Culture Manager rolunuzu gordum. Telecommunications tarafinda kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>Subject: Vodafone Turkey ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Tolga,
-Vodafone Turkey ekibinin Telecommunications ölçeğinde global ekiplerle yoğun iş birliği odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Global ekiplerle yoğun iş birliği nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Vodafone Turkey için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Turkcell ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Asli,
+Turkcell ekibinin Telecommunications olceginde kurumsal donusum ve teknoloji yetkinlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Turkcell icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M72" t="str">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>Can Yilmaz</x:v>
+        <x:v>Deniz Ozdemir</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>Eczacibasi</x:v>
+        <x:v>Insider</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D73" t="str"/>
       <x:c r="E73" t="str"/>
       <x:c r="F73" t="str">
-        <x:v>Conglomerate / Healthcare / Industry</x:v>
+        <x:v>B2B SaaS / MarTech</x:v>
       </x:c>
       <x:c r="G73" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H73" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>84</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J73" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>Merhaba Can, Eczacibasi için People and Culture Manager rolünüzü gördüm. Conglomerate / Healthcare / Industry tarafında çok sektörlü yetenek gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Deniz, Insider icin Talent Management Specialist rolunuzu gordum. B2B SaaS / MarTech tarafinda global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L73" t="str">
-        <x:v>Subject: Eczacibasi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Eczacibasi ekibinin Conglomerate / Healthcare / Industry ölçeğinde çok sektörlü yetenek gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Eczacibasi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Insider ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Deniz,
+Insider ekibinin B2B SaaS / MarTech olceginde global SaaS satis, musteri basarisi ve urun ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global SaaS satis, musteri basarisi ve urun ekipleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Insider icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M73" t="str">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>Gizem Celik</x:v>
+        <x:v>Deniz Ozdemir</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>Papara</x:v>
+        <x:v>Trendyol</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D74" t="str"/>
       <x:c r="E74" t="str"/>
       <x:c r="F74" t="str">
-        <x:v>Fintech</x:v>
+        <x:v>E-commerce / Marketplace</x:v>
       </x:c>
       <x:c r="G74" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H74" t="str">
-        <x:v>fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J74" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>Merhaba Gizem, Papara için Talent Management Specialist rolünüzü gördüm. Fintech tarafında fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Deniz, Trendyol icin Insan Kaynaklari Uzmani rolunuzu gordum. E-commerce / Marketplace tarafinda hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L74" t="str">
-        <x:v>Subject: Papara ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Gizem,
-Papara ekibinin Fintech ölçeğinde fintech büyümesi ve regülasyonla uyumlu ekipler odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Fintech büyümesi ve regülasyonla uyumlu ekipler nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Papara için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Trendyol ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Deniz,
+Trendyol ekibinin E-commerce / Marketplace olceginde hizli olceklenen ekipler ve uluslararasi operasyon odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Trendyol icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M74" t="str">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>Emre Demir</x:v>
+        <x:v>Mert Yilmaz</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Getir</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D75" t="str"/>
       <x:c r="E75" t="str"/>
       <x:c r="F75" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Quick commerce / Delivery</x:v>
       </x:c>
       <x:c r="G75" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H75" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>Merhaba Emre, Dream Games için Talent Acquisition Manager rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, Getir icin Organizational Development Manager rolunuzu gordum. Quick commerce / Delivery tarafinda cok lokasyonlu operasyon ve saha ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L75" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Getir ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mert,
+Getir ekibinin Quick commerce / Delivery olceginde cok lokasyonlu operasyon ve saha ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Getir icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M75" t="str">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>Ece Aydin</x:v>
+        <x:v>Tolga Kara</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D76" t="str"/>
       <x:c r="E76" t="str"/>
       <x:c r="F76" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G76" t="str">
         <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H76" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>Merhaba Ece, Yemeksepeti için HR Business Partner rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Mavi icin Talent Acquisition Manager rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L76" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ece,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M76" t="str">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>Derya Demir</x:v>
+        <x:v>Gizem Yilmaz</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Logo Yazilim</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Insan Kaynaklari Uzmani</x:v>
       </x:c>
       <x:c r="D77" t="str"/>
       <x:c r="E77" t="str"/>
       <x:c r="F77" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>B2B SaaS / Software</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H77" t="str">
-        <x:v>üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>78</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>Merhaba Derya, Ford Otosan için Talent Management Specialist rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Logo Yazilim icin Insan Kaynaklari Uzmani rolunuzu gordum. B2B SaaS / Software tarafinda teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L77" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Derya,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Logo Yazilim ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Logo Yazilim ekibinin B2B SaaS / Software olceginde teknoloji yetenekleri ve musteri odakli ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: teknoloji yetenekleri ve musteri odakli ekipler nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Logo Yazilim icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M77" t="str">
-        <x:v>78</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>Mehmet Kaya</x:v>
+        <x:v>Can Arslan</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>Dream Games</x:v>
+        <x:v>Garanti BBVA</x:v>
       </x:c>
       <x:c r="C78" t="str">
         <x:v>HR Business Partner</x:v>
@@ -3514,260 +3514,260 @@
       <x:c r="D78" t="str"/>
       <x:c r="E78" t="str"/>
       <x:c r="F78" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G78" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H78" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>Merhaba Mehmet, Dream Games için HR Business Partner rolünüzü gördüm. Gaming / Technology tarafında global ürün ekipleri ve hızlı işe alım nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Can, Garanti BBVA icin HR Business Partner rolunuzu gordum. Banking / Finance tarafinda global bankacilik standartlari ve dijitallesme nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L78" t="str">
-        <x:v>Subject: Dream Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mehmet,
-Dream Games ekibinin Gaming / Technology ölçeğinde global ürün ekipleri ve hızlı işe alım odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Dream Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Garanti BBVA ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Can,
+Garanti BBVA ekibinin Banking / Finance olceginde global bankacilik standartlari ve dijitallesme odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Garanti BBVA icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M78" t="str">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>Can Erdem</x:v>
+        <x:v>Ceren Celik</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>Colendi</x:v>
+        <x:v>Trendyol</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D79" t="str"/>
       <x:c r="E79" t="str"/>
       <x:c r="F79" t="str">
-        <x:v>Fintech</x:v>
+        <x:v>E-commerce / Marketplace</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H79" t="str">
-        <x:v>uluslararası fintech ürünleşmesi nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>Merhaba Can, Colendi için Human Resources Director rolünüzü gördüm. Fintech tarafında uluslararası fintech ürünleşmesi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Uluslararası fintech ürünleşmesi nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Trendyol icin Employee Experience Lead rolunuzu gordum. E-commerce / Marketplace tarafinda hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L79" t="str">
-        <x:v>Subject: Colendi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Colendi ekibinin Fintech ölçeğinde uluslararası fintech ürünleşmesi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Uluslararası fintech ürünleşmesi nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Colendi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Trendyol ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Trendyol ekibinin E-commerce / Marketplace olceginde hizli olceklenen ekipler ve uluslararasi operasyon odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Trendyol icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M79" t="str">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>Mert Yilmaz</x:v>
+        <x:v>Mert Celik</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Dream Games</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>HR Business Partner</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D80" t="str"/>
       <x:c r="E80" t="str"/>
       <x:c r="F80" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Gaming / Technology</x:v>
       </x:c>
       <x:c r="G80" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H80" t="str">
-        <x:v>Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek</x:v>
+        <x:v>global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>76</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>Merhaba Mert, Yemeksepeti için HR Business Partner rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, Dream Games icin Insan Kaynaklari Muduru rolunuzu gordum. Gaming / Technology tarafinda global urun ekipleri ve hizli ise alim nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L80" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
+        <x:v>Subject: Dream Games ekipleri icin konusma odakli Ingilizce pilotu
 Merhaba Mert,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Farklı ekiplerin İngilizce ihtiyacını tek modelde önceliklendirmek.
-Konuşarak Öğren ile 'Departman bazlı İngilizce ihtiyacını HRBP perspektifiyle haritalama' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+Dream Games ekibinin Gaming / Technology olceginde global urun ekipleri ve hizli ise alim odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: global urun ekipleri ve hizli ise alim nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Dream Games icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M80" t="str">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>Asli Aydin</x:v>
+        <x:v>Ayse Bulut</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>Eczacibasi</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D81" t="str"/>
       <x:c r="E81" t="str"/>
       <x:c r="F81" t="str">
-        <x:v>Conglomerate / Healthcare / Industry</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G81" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H81" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>Merhaba Asli, Eczacibasi için Organizational Development Manager rolünüzü gördüm. Conglomerate / Healthcare / Industry tarafında çok sektörlü yetenek gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ayse, Isbank icin Talent Acquisition Manager rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L81" t="str">
-        <x:v>Subject: Eczacibasi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Asli,
-Eczacibasi ekibinin Conglomerate / Healthcare / Industry ölçeğinde çok sektörlü yetenek gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Eczacibasi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ayse,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M81" t="str">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
-        <x:v>Zeynep Acar</x:v>
+        <x:v>Derya Bulut</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>Peak Games</x:v>
+        <x:v>Sabanci Holding</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D82" t="str"/>
       <x:c r="E82" t="str"/>
       <x:c r="F82" t="str">
-        <x:v>Gaming / Technology</x:v>
+        <x:v>Conglomerate</x:v>
       </x:c>
       <x:c r="G82" t="str">
-        <x:v>250-1000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H82" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J82" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Merhaba Zeynep, Peak Games için Talent Acquisition Manager rolünüzü gördüm. Gaming / Technology tarafında global ürün ve çok uluslu çalışma ritmi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Sabanci Holding icin Human Resources Director rolunuzu gordum. Conglomerate tarafinda globallesme ve liderlik gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L82" t="str">
-        <x:v>Subject: Peak Games ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Peak Games ekibinin Gaming / Technology ölçeğinde global ürün ve çok uluslu çalışma ritmi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Peak Games için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Sabanci Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Sabanci Holding ekibinin Conglomerate olceginde globallesme ve liderlik gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: globallesme ve liderlik gelisimi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Sabanci Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M82" t="str">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
-        <x:v>Gizem Aslan</x:v>
+        <x:v>Mehmet Kaya</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>Trendyol</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D83" t="str"/>
       <x:c r="E83" t="str"/>
       <x:c r="F83" t="str">
-        <x:v>E-commerce / Marketplace</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G83" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H83" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Merhaba Gizem, Trendyol için People and Culture Manager rolünüzü gördüm. E-commerce / Marketplace tarafında hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mehmet, Isbank icin Human Resources Director rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>Subject: Trendyol ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Gizem,
-Trendyol ekibinin E-commerce / Marketplace ölçeğinde hızlı ölçeklenen ekipler ve uluslararası operasyon odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Trendyol için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mehmet,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
-        <x:v>Deniz Ozdemir</x:v>
+        <x:v>Berk Kaya</x:v>
       </x:c>
       <x:c r="B84" t="str">
         <x:v>Koc Holding</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D84" t="str"/>
       <x:c r="E84" t="str"/>
@@ -3778,23 +3778,23 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H84" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I84" t="str">
         <x:v>89</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Merhaba Deniz, Koc Holding için People and Culture Manager rolünüzü gördüm. Conglomerate tarafında grup şirketleri arası ortak gelişim programları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Koc Holding icin Talent Acquisition Manager rolunuzu gordum. Conglomerate tarafinda grup sirketleri arasi ortak gelisim programlari nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L84" t="str">
-        <x:v>Subject: Koc Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Deniz,
-Koc Holding ekibinin Conglomerate ölçeğinde grup şirketleri arası ortak gelişim programları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Koc Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Koc Holding ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Koc Holding ekibinin Conglomerate olceginde grup sirketleri arasi ortak gelisim programlari odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Koc Holding icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -3804,56 +3804,56 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>Ayse Kara</x:v>
+        <x:v>Gizem Demir</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Turkcell</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D85" t="str"/>
       <x:c r="E85" t="str"/>
       <x:c r="F85" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Telecommunications</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H85" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>Merhaba Ayse, Yemeksepeti için Talent Management Specialist rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Turkcell icin Organizational Development Manager rolunuzu gordum. Telecommunications tarafinda kurumsal donusum ve teknoloji yetkinlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ayse,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Turkcell ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Turkcell ekibinin Telecommunications olceginde kurumsal donusum ve teknoloji yetkinlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Turkcell icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M85" t="str">
-        <x:v>75</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>Burak Ozdemir</x:v>
+        <x:v>Selin Ozdemir</x:v>
       </x:c>
       <x:c r="B86" t="str">
         <x:v>Eczacibasi</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D86" t="str"/>
       <x:c r="E86" t="str"/>
@@ -3864,23 +3864,23 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H86" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I86" t="str">
         <x:v>84</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>Merhaba Burak, Eczacibasi için Talent Acquisition Manager rolünüzü gördüm. Conglomerate / Healthcare / Industry tarafında çok sektörlü yetenek gelişimi nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Eczacibasi icin Organizational Development Manager rolunuzu gordum. Conglomerate / Healthcare / Industry tarafinda cok sektorlu yetenek gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L86" t="str">
-        <x:v>Subject: Eczacibasi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Burak,
-Eczacibasi ekibinin Conglomerate / Healthcare / Industry ölçeğinde çok sektörlü yetenek gelişimi odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Eczacibasi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Eczacibasi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Eczacibasi ekibinin Conglomerate / Healthcare / Industry olceginde cok sektorlu yetenek gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Eczacibasi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -3890,83 +3890,83 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>Zeynep Koc</x:v>
+        <x:v>Ceren Sahin</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D87" t="str"/>
       <x:c r="E87" t="str"/>
       <x:c r="F87" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G87" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H87" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>Merhaba Zeynep, Ford Otosan için Talent Acquisition Manager rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Ceren, Isbank icin Insan Kaynaklari Muduru rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L87" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Zeynep,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Ceren,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M87" t="str">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>Ece Erdem</x:v>
+        <x:v>Elif Bulut</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Talent Management Specialist</x:v>
       </x:c>
       <x:c r="D88" t="str"/>
       <x:c r="E88" t="str"/>
       <x:c r="F88" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G88" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H88" t="str">
-        <x:v>operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>Merhaba Ece, Yemeksepeti için Human Resources Director rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Isbank icin Talent Management Specialist rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L88" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ece,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
@@ -3976,271 +3976,271 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>Emre Arslan</x:v>
+        <x:v>Elif Ozturk</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>Arcelik</x:v>
+        <x:v>Colendi</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D89" t="str"/>
       <x:c r="E89" t="str"/>
       <x:c r="F89" t="str">
-        <x:v>Consumer durables / Manufacturing</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G89" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H89" t="str">
-        <x:v>global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J89" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>Merhaba Emre, Arcelik için Human Resources Director rolünüzü gördüm. Consumer durables / Manufacturing tarafında global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Elif, Colendi icin Insan Kaynaklari Muduru rolunuzu gordum. Fintech tarafinda uluslararasi fintech urunlesmesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L89" t="str">
-        <x:v>Subject: Arcelik ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Emre,
-Arcelik ekibinin Consumer durables / Manufacturing ölçeğinde global marka ve çok ülkeli ekip yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Global marka ve çok ülkeli ekip yapısı nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Arcelik için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Colendi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Elif,
+Colendi ekibinin Fintech olceginde uluslararasi fintech urunlesmesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: uluslararasi fintech urunlesmesi nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Colendi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M89" t="str">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>Gizem Kilic</x:v>
+        <x:v>Mehmet Sahin</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>Koc Holding</x:v>
+        <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>People and Culture Manager</x:v>
+        <x:v>Human Resources Director</x:v>
       </x:c>
       <x:c r="D90" t="str"/>
       <x:c r="E90" t="str"/>
       <x:c r="F90" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H90" t="str">
-        <x:v>Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak</x:v>
+        <x:v>perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>89</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>Merhaba Gizem, Koc Holding için People and Culture Manager rolünüzü gördüm. Conglomerate tarafında grup şirketleri arası ortak gelişim programları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mehmet, Mavi icin Human Resources Director rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L90" t="str">
-        <x:v>Subject: Koc Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Gizem,
-Koc Holding ekibinin Conglomerate ölçeğinde grup şirketleri arası ortak gelişim programları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışan bağlılığını artıran, kişiye özel gelişim benefit'i sunmak.
-Konuşarak Öğren ile 'Çalışan deneyimi benefit'i olarak esnek İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Koc Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mehmet,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M90" t="str">
-        <x:v>93</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>Can Kara</x:v>
+        <x:v>Derya Bulut</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>Trendyol</x:v>
+        <x:v>Eczacibasi</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>Talent Acquisition Manager</x:v>
+        <x:v>Organizational Development Manager</x:v>
       </x:c>
       <x:c r="D91" t="str"/>
       <x:c r="E91" t="str"/>
       <x:c r="F91" t="str">
-        <x:v>E-commerce / Marketplace</x:v>
+        <x:v>Conglomerate / Healthcare / Industry</x:v>
       </x:c>
       <x:c r="G91" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H91" t="str">
-        <x:v>Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I91" t="str">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>Merhaba Derya, Eczacibasi icin Organizational Development Manager rolunuzu gordum. Conglomerate / Healthcare / Industry tarafinda cok sektorlu yetenek gelisimi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
+      </x:c>
+      <x:c r="L91" t="str">
+        <x:v>Subject: Eczacibasi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Eczacibasi ekibinin Conglomerate / Healthcare / Industry olceginde cok sektorlu yetenek gelisimi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Eczacibasi icin mantikli pilot segmentini birlikte cikaralim.
+Sevgiler,
+Growth Automation Ekibi</x:v>
+      </x:c>
+      <x:c r="M91" t="str">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="J91" t="str">
-        <x:v>Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi</x:v>
-      </x:c>
-      <x:c r="K91" t="str">
-        <x:v>Merhaba Can, Trendyol için Talent Acquisition Manager rolünüzü gördüm. E-commerce / Marketplace tarafında hızlı ölçeklenen ekipler ve uluslararası operasyon nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
-      </x:c>
-      <x:c r="L91" t="str">
-        <x:v>Subject: Trendyol ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Trendyol ekibinin E-commerce / Marketplace ölçeğinde hızlı ölçeklenen ekipler ve uluslararası operasyon odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Aday deneyiminde İngilizce değerlendirme ve global rol iletişimini standardize etmek.
-Konuşarak Öğren ile 'Global aday ve ekip iletişimi için konuşma odaklı İngilizce gelişimi' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Trendyol için mantıklı pilot segmentini birlikte çıkaralım.
-Sevgiler,
-Growth Automation Ekibi</x:v>
-      </x:c>
-      <x:c r="M91" t="str">
-        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>Ece Kilic</x:v>
+        <x:v>Asli Ozturk</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Yemeksepeti</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D92" t="str"/>
       <x:c r="E92" t="str"/>
       <x:c r="F92" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Food delivery / Tech</x:v>
       </x:c>
       <x:c r="G92" t="str">
-        <x:v>5000+</x:v>
+        <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H92" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>Merhaba Ece, Yapi Kredi için Organizational Development Manager rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Asli, Yemeksepeti icin Talent Acquisition Manager rolunuzu gordum. Food delivery / Tech tarafinda operasyon, satis ve teknoloji ekipleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L92" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ece,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yemeksepeti ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Asli,
+Yemeksepeti ekibinin Food delivery / Tech olceginde operasyon, satis ve teknoloji ekipleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yemeksepeti icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M92" t="str">
-        <x:v>86</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>Mert Kaplan</x:v>
+        <x:v>Derya Arslan</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>Vestel</x:v>
+        <x:v>Papara</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D93" t="str"/>
       <x:c r="E93" t="str"/>
       <x:c r="F93" t="str">
-        <x:v>Electronics / Manufacturing</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G93" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H93" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J93" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>Merhaba Mert, Vestel için Organizational Development Manager rolünüzü gördüm. Electronics / Manufacturing tarafında ihracat ağı ve teknik ekiplerin İngilizce ihtiyacı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Derya, Papara icin Learning and Development Manager rolunuzu gordum. Fintech tarafinda fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L93" t="str">
-        <x:v>Subject: Vestel ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Mert,
-Vestel ekibinin Electronics / Manufacturing ölçeğinde ihracat ağı ve teknik ekiplerin İngilizce ihtiyacı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Vestel için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Papara ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Derya,
+Papara ekibinin Fintech olceginde fintech buyumesi ve regulasyonla uyumlu ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Papara icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M93" t="str">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>Can Kara</x:v>
+        <x:v>Mert Kaya</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>Koc Holding</x:v>
+        <x:v>Trendyol</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>People and Culture Manager</x:v>
       </x:c>
       <x:c r="D94" t="str"/>
       <x:c r="E94" t="str"/>
       <x:c r="F94" t="str">
-        <x:v>Conglomerate</x:v>
+        <x:v>E-commerce / Marketplace</x:v>
       </x:c>
       <x:c r="G94" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H94" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>Merhaba Can, Koc Holding için Organizational Development Manager rolünüzü gördüm. Conglomerate tarafında grup şirketleri arası ortak gelişim programları nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Mert, Trendyol icin People and Culture Manager rolunuzu gordum. E-commerce / Marketplace tarafinda hizli olceklenen ekipler ve uluslararasi operasyon nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L94" t="str">
-        <x:v>Subject: Koc Holding ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Koc Holding ekibinin Conglomerate ölçeğinde grup şirketleri arası ortak gelişim programları odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Koc Holding için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Trendyol ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Mert,
+Trendyol ekibinin E-commerce / Marketplace olceginde hizli olceklenen ekipler ve uluslararasi operasyon odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Trendyol icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M94" t="str">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>Derya Bulut</x:v>
+        <x:v>Gizem Celik</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D95" t="str"/>
       <x:c r="E95" t="str"/>
@@ -4251,39 +4251,39 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H95" t="str">
-        <x:v>şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J95" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>Merhaba Derya, Yapi Kredi için Talent Management Specialist rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Gizem, Isbank icin Employee Experience Lead rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L95" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Derya,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Gizem,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M95" t="str">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>Onur Ozturk</x:v>
+        <x:v>Burak Yildiz</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>Garanti BBVA</x:v>
+        <x:v>Akbank</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>Organizational Development Manager</x:v>
+        <x:v>Learning and Development Manager</x:v>
       </x:c>
       <x:c r="D96" t="str"/>
       <x:c r="E96" t="str"/>
@@ -4294,165 +4294,165 @@
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H96" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J96" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>Merhaba Onur, Garanti BBVA için Organizational Development Manager rolünüzü gördüm. Banking / Finance tarafında global bankacılık standartları ve dijitalleşme nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Burak, Akbank icin Learning and Development Manager rolunuzu gordum. Banking / Finance tarafinda dijital bankacilik ve yetenek donusumu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L96" t="str">
-        <x:v>Subject: Garanti BBVA ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Onur,
-Garanti BBVA ekibinin Banking / Finance ölçeğinde global bankacılık standartları ve dijitalleşme odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Garanti BBVA için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Akbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Burak,
+Akbank ekibinin Banking / Finance olceginde dijital bankacilik ve yetenek donusumu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Akbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M96" t="str">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>Ece Aslan</x:v>
+        <x:v>Tolga Acar</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>Turkcell</x:v>
+        <x:v>Tofas</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>HR Business Partner</x:v>
       </x:c>
       <x:c r="D97" t="str"/>
       <x:c r="E97" t="str"/>
       <x:c r="F97" t="str">
-        <x:v>Telecommunications</x:v>
+        <x:v>Automotive / Manufacturing</x:v>
       </x:c>
       <x:c r="G97" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H97" t="str">
-        <x:v>kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>Merhaba Ece, Turkcell için Human Resources Director rolünüzü gördüm. Telecommunications tarafında kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Tolga, Tofas icin HR Business Partner rolunuzu gordum. Automotive / Manufacturing tarafinda mavi yaka, beyaz yaka ve global partner dengesi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L97" t="str">
-        <x:v>Subject: Turkcell ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ece,
-Turkcell ekibinin Telecommunications ölçeğinde kurumsal dönüşüm ve teknoloji yetkinlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Kurumsal dönüşüm ve teknoloji yetkinlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Turkcell için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Tofas ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Tolga,
+Tofas ekibinin Automotive / Manufacturing olceginde mavi yaka, beyaz yaka ve global partner dengesi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Farkli ekiplerin Ingilizce ihtiyacini tek modelde onceliklendirmek.
+Konusarak Ogren ile 'Departman bazli Ingilizce ihtiyacini HRBP perspektifiyle haritalama' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Tofas icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M97" t="str">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="str">
-        <x:v>Ceren Koc</x:v>
+        <x:v>Irem Kaya</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>Mavi</x:v>
+        <x:v>Isbank</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>Talent Management Specialist</x:v>
+        <x:v>Employee Experience Lead</x:v>
       </x:c>
       <x:c r="D98" t="str"/>
       <x:c r="E98" t="str"/>
       <x:c r="F98" t="str">
-        <x:v>Retail / Fashion</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G98" t="str">
-        <x:v>1000-5000</x:v>
+        <x:v>5000+</x:v>
       </x:c>
       <x:c r="H98" t="str">
-        <x:v>perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J98" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>Merhaba Ceren, Mavi için Talent Management Specialist rolünüzü gördüm. Retail / Fashion tarafında perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Irem, Isbank icin Employee Experience Lead rolunuzu gordum. Banking / Finance tarafinda kurumsal olcekte egitim standardizasyonu nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L98" t="str">
-        <x:v>Subject: Mavi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Ceren,
-Mavi ekibinin Retail / Fashion ölçeğinde perakende ekipleri ve marka iş birlikleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Perakende ekipleri ve marka iş birlikleri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Mavi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Isbank ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Irem,
+Isbank ekibinin Banking / Finance olceginde kurumsal olcekte egitim standardizasyonu odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisan bagliligini artiran, kisiye ozel gelisim benefit'i sunmak.
+Konusarak Ogren ile 'Calisan deneyimi benefit'i olarak esnek Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Isbank icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M98" t="str">
-        <x:v>69</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="str">
-        <x:v>Berk Acar</x:v>
+        <x:v>Irem Kaya</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>Yapi Kredi</x:v>
+        <x:v>Papara</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Insan Kaynaklari Muduru</x:v>
       </x:c>
       <x:c r="D99" t="str"/>
       <x:c r="E99" t="str"/>
       <x:c r="F99" t="str">
-        <x:v>Banking / Finance</x:v>
+        <x:v>Fintech</x:v>
       </x:c>
       <x:c r="G99" t="str">
-        <x:v>5000+</x:v>
+        <x:v>250-1000</x:v>
       </x:c>
       <x:c r="H99" t="str">
-        <x:v>şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J99" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Kurumsal Ingilizce gelisimini hizli pilotla test etme</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>Merhaba Berk, Yapi Kredi için Human Resources Director rolünüzü gördüm. Banking / Finance tarafında şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Irem, Papara icin Insan Kaynaklari Muduru rolunuzu gordum. Fintech tarafinda fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L99" t="str">
-        <x:v>Subject: Yapi Kredi ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Berk,
-Yapi Kredi ekibinin Banking / Finance ölçeğinde şube, merkez ve teknoloji ekiplerinin karma yapısı odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Şube, merkez ve teknoloji ekiplerinin karma yapısı nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yapi Kredi için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Papara ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Irem,
+Papara ekibinin Fintech olceginde fintech buyumesi ve regulasyonla uyumlu ekipler odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: fintech buyumesi ve regulasyonla uyumlu ekipler nedeniyle Ingilizce gelisim programini olceklendirmek.
+Konusarak Ogren ile 'Kurumsal Ingilizce gelisimini hizli pilotla test etme' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Papara icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M99" t="str">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>Elif Polat</x:v>
+        <x:v>Selin Kara</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>Yemeksepeti</x:v>
+        <x:v>Mavi</x:v>
       </x:c>
       <x:c r="C100" t="str">
         <x:v>Learning and Development Manager</x:v>
@@ -4460,77 +4460,77 @@
       <x:c r="D100" t="str"/>
       <x:c r="E100" t="str"/>
       <x:c r="F100" t="str">
-        <x:v>Food delivery / Tech</x:v>
+        <x:v>Retail / Fashion</x:v>
       </x:c>
       <x:c r="G100" t="str">
         <x:v>1000-5000</x:v>
       </x:c>
       <x:c r="H100" t="str">
-        <x:v>Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak</x:v>
+        <x:v>Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak</x:v>
       </x:c>
       <x:c r="I100" t="str">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J100" t="str">
-        <x:v>L&amp;D programlarına ölçülebilir konuşma pratiği katmanı</x:v>
+        <x:v>L&amp;D programlarina olculebilir konusma pratigi katmani</x:v>
       </x:c>
       <x:c r="K100" t="str">
-        <x:v>Merhaba Elif, Yemeksepeti için Learning and Development Manager rolünüzü gördüm. Food delivery / Tech tarafında operasyon, satış ve teknoloji ekipleri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Selin, Mavi icin Learning and Development Manager rolunuzu gordum. Retail / Fashion tarafinda perakende ekipleri ve marka is birlikleri nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'L&amp;D programlarina olculebilir konusma pratigi katmani' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L100" t="str">
-        <x:v>Subject: Yemeksepeti ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Elif,
-Yemeksepeti ekibinin Food delivery / Tech ölçeğinde operasyon, satış ve teknoloji ekipleri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Çalışanlara ölçülebilir, ölçeklenebilir ve yoğun programa uyumlu İngilizce gelişim yolu kurmak.
-Konuşarak Öğren ile 'L&amp;D programlarına ölçülebilir konuşma pratiği katmanı' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Yemeksepeti için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Mavi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Selin,
+Mavi ekibinin Retail / Fashion olceginde perakende ekipleri ve marka is birlikleri odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Calisanlara olculebilir, olceklenebilir ve yogun programa uyumlu Ingilizce gelisim yolu kurmak.
+Konusarak Ogren ile 'L&amp;D programlarina olculebilir konusma pratigi katmani' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Mavi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M100" t="str">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="str">
-        <x:v>Can Kaya</x:v>
+        <x:v>Berk Ozturk</x:v>
       </x:c>
       <x:c r="B101" t="str">
-        <x:v>Ford Otosan</x:v>
+        <x:v>Yapi Kredi</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>Human Resources Director</x:v>
+        <x:v>Talent Acquisition Manager</x:v>
       </x:c>
       <x:c r="D101" t="str"/>
       <x:c r="E101" t="str"/>
       <x:c r="F101" t="str">
-        <x:v>Automotive / Manufacturing</x:v>
+        <x:v>Banking / Finance</x:v>
       </x:c>
       <x:c r="G101" t="str">
         <x:v>5000+</x:v>
       </x:c>
       <x:c r="H101" t="str">
-        <x:v>üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek</x:v>
+        <x:v>Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek</x:v>
       </x:c>
       <x:c r="I101" t="str">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>Kurumsal İngilizce gelişimini hızlı pilotla test etme</x:v>
+        <x:v>Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi</x:v>
       </x:c>
       <x:c r="K101" t="str">
-        <x:v>Merhaba Can, Ford Otosan için Human Resources Director rolünüzü gördüm. Automotive / Manufacturing tarafında üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce iletişim kritik hale geliyor. Konuşarak Öğren'de 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' başlığıyla 2 haftalık küçük bir pilot kurguluyoruz. Eğer 'Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek' gündeminizdeyse 15 dk fikir alışverişi yapmak isterim.</x:v>
+        <x:v>Merhaba Berk, Yapi Kredi icin Talent Acquisition Manager rolunuzu gordum. Banking / Finance tarafinda sube, merkez ve teknoloji ekiplerinin karma yapisi nedeniyle Ingilizce iletisim kritik hale geliyor. Konusarak Ogren'de 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' basligiyla 2 haftalik kucuk bir pilot kurguluyoruz. Eger 'Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek' gundeminizdeyse 15 dk fikir alisverisi yapmak isterim.</x:v>
       </x:c>
       <x:c r="L101" t="str">
-        <x:v>Subject: Ford Otosan ekipleri için konuşma odaklı İngilizce pilotu
-Merhaba Can,
-Ford Otosan ekibinin Automotive / Manufacturing ölçeğinde üretim, mühendislik ve global tedarik zinciri odağı olduğunu görüyorum. Bu yapıdaki HR ekiplerinde sık gördüğümüz konu: Üretim, mühendislik ve global tedarik zinciri nedeniyle İngilizce gelişim programını ölçeklemek.
-Konuşarak Öğren ile 'Kurumsal İngilizce gelişimini hızlı pilotla test etme' üzerine düşük eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup seçimi, konuşma pratiği ve kısa gelişim raporu.
-Uygunsa bu hafta 15 dakikalık bir görüşmede Ford Otosan için mantıklı pilot segmentini birlikte çıkaralım.
+        <x:v>Subject: Yapi Kredi ekipleri icin konusma odakli Ingilizce pilotu
+Merhaba Berk,
+Yapi Kredi ekibinin Banking / Finance olceginde sube, merkez ve teknoloji ekiplerinin karma yapisi odagi oldugunu goruyorum. Bu yapidaki HR ekiplerinde sik gordugumuz konu: Aday deneyiminde Ingilizce degerlendirme ve global rol iletisimini standardize etmek.
+Konusarak Ogren ile 'Global aday ve ekip iletisimi icin konusma odakli Ingilizce gelisimi' uzerine dusuk eforlu bir pilot tasarlayabiliriz: seviye tespiti, hedef grup secimi, konusma pratigi ve kisa gelisim raporu.
+Uygunsa bu hafta 15 dakikalik bir gorusmede Yapi Kredi icin mantikli pilot segmentini birlikte cikaralim.
 Sevgiler,
 Growth Automation Ekibi</x:v>
       </x:c>
       <x:c r="M101" t="str">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
